--- a/data/trans_dic/MCS12_SP_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 21,53</t>
+          <t>14,21; 21,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,14; 20,74</t>
+          <t>13,26; 20,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,38</t>
+          <t>13,85; 21,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,93</t>
+          <t>14,62; 21,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,9; 27,0</t>
+          <t>17,58; 27,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,09; 28,23</t>
+          <t>18,05; 28,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 22,52</t>
+          <t>14,41; 22,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 26,58</t>
+          <t>19,28; 26,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 22,39</t>
+          <t>16,85; 22,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 22,06</t>
+          <t>16,05; 22,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 20,86</t>
+          <t>14,95; 20,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 22,88</t>
+          <t>18,18; 23,14</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,0; 18,42</t>
+          <t>11,3; 18,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 25,17</t>
+          <t>17,13; 25,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 21,26</t>
+          <t>12,86; 20,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,71; 19,86</t>
+          <t>12,96; 19,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,64; 30,82</t>
+          <t>21,68; 30,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 38,37</t>
+          <t>27,18; 38,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,27; 28,84</t>
+          <t>19,93; 28,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,98; 28,52</t>
+          <t>21,17; 28,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,4; 23,48</t>
+          <t>17,8; 23,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,66; 29,71</t>
+          <t>22,66; 29,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,71; 23,62</t>
+          <t>17,61; 23,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,88</t>
+          <t>17,69; 22,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 21,62</t>
+          <t>14,74; 21,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,98; 29,64</t>
+          <t>22,35; 29,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,83; 25,46</t>
+          <t>18,28; 25,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 24,36</t>
+          <t>5,07; 24,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 31,58</t>
+          <t>19,28; 32,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,74; 41,06</t>
+          <t>28,77; 41,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,16; 38,51</t>
+          <t>24,53; 39,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 31,64</t>
+          <t>21,07; 31,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 22,91</t>
+          <t>16,85; 22,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,22; 31,54</t>
+          <t>25,0; 31,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,37; 27,11</t>
+          <t>20,8; 27,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 25,2</t>
+          <t>8,34; 25,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,69; 24,52</t>
+          <t>19,73; 24,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 27,07</t>
+          <t>21,97; 27,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,41</t>
+          <t>17,48; 22,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 24,31</t>
+          <t>18,49; 24,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 29,76</t>
+          <t>23,18; 30,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,89; 33,49</t>
+          <t>26,64; 33,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 29,92</t>
+          <t>23,57; 29,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,03; 68,69</t>
+          <t>24,2; 68,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,69; 25,63</t>
+          <t>22,0; 25,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,59; 28,97</t>
+          <t>24,44; 28,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,8; 24,76</t>
+          <t>20,87; 24,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,93; 51,56</t>
+          <t>21,89; 53,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 24,8</t>
+          <t>15,53; 24,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 26,85</t>
+          <t>19,48; 26,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 24,0</t>
+          <t>17,66; 24,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 27,4</t>
+          <t>19,07; 27,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,76; 33,09</t>
+          <t>25,36; 33,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,27; 42,43</t>
+          <t>35,78; 42,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,39; 38,46</t>
+          <t>31,56; 38,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,27; 32,92</t>
+          <t>22,44; 33,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,67; 28,43</t>
+          <t>23,05; 28,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,53</t>
+          <t>29,94; 35,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,8; 31,07</t>
+          <t>25,8; 30,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,03; 29,81</t>
+          <t>21,84; 29,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,2</t>
+          <t>8,64; 15,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,22; 19,88</t>
+          <t>11,5; 20,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 14,79</t>
+          <t>7,63; 15,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,52</t>
+          <t>6,0; 16,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,2; 29,21</t>
+          <t>24,17; 29,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,55; 35,5</t>
+          <t>29,92; 35,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,98; 27,43</t>
+          <t>21,66; 27,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,0; 32,07</t>
+          <t>25,68; 32,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,37; 25,92</t>
+          <t>21,52; 25,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,69; 31,77</t>
+          <t>26,89; 31,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,24; 23,96</t>
+          <t>19,36; 23,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,34; 26,8</t>
+          <t>21,46; 26,96</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,35; 20,04</t>
+          <t>17,22; 19,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,78; 23,69</t>
+          <t>20,82; 23,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,51; 20,25</t>
+          <t>17,57; 20,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,13; 20,14</t>
+          <t>14,24; 20,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,01; 27,99</t>
+          <t>25,05; 28,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,14; 34,29</t>
+          <t>31,06; 34,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,29; 28,38</t>
+          <t>25,38; 28,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,94; 45,66</t>
+          <t>25,87; 46,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,71; 23,63</t>
+          <t>21,66; 23,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,41; 28,7</t>
+          <t>26,45; 28,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,81; 23,91</t>
+          <t>21,96; 24,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,7; 33,97</t>
+          <t>21,57; 32,25</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66624; 102025</t>
+          <t>67341; 101865</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57443; 90671</t>
+          <t>57989; 88889</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59089; 91737</t>
+          <t>59438; 91561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75364; 110333</t>
+          <t>73541; 109618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54893; 82814</t>
+          <t>53914; 84008</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56891; 88762</t>
+          <t>56763; 88909</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48304; 78140</t>
+          <t>50022; 79003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89105; 118572</t>
+          <t>86036; 117409</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131323; 174775</t>
+          <t>131493; 174785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119157; 165834</t>
+          <t>120640; 167248</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119229; 161911</t>
+          <t>116062; 160469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>173146; 217227</t>
+          <t>172613; 219606</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40362; 67583</t>
+          <t>41460; 69162</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68860; 105418</t>
+          <t>71759; 106936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49637; 80197</t>
+          <t>48514; 79188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57363; 89672</t>
+          <t>58497; 88785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80489; 114625</t>
+          <t>80618; 113906</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91367; 129685</t>
+          <t>91855; 129198</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75474; 107360</t>
+          <t>74199; 107625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80138; 108964</t>
+          <t>80877; 109292</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128541; 173444</t>
+          <t>131519; 175646</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171491; 224825</t>
+          <t>171501; 222581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132747; 177039</t>
+          <t>131962; 176974</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>147009; 190728</t>
+          <t>147465; 188797</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81901; 117247</t>
+          <t>79965; 116762</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>138363; 186549</t>
+          <t>140655; 183635</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93055; 132866</t>
+          <t>95414; 132382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31680; 162054</t>
+          <t>33728; 165268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29605; 52986</t>
+          <t>32353; 54346</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74750; 106812</t>
+          <t>74846; 107342</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40140; 63967</t>
+          <t>40756; 66396</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35130; 52503</t>
+          <t>34966; 51584</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120818; 162672</t>
+          <t>119675; 162494</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224362; 280523</t>
+          <t>222373; 279827</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140141; 186529</t>
+          <t>143126; 187920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61709; 209467</t>
+          <t>69359; 209286</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>243811; 303669</t>
+          <t>244263; 297787</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252050; 313792</t>
+          <t>254655; 315669</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>202789; 257685</t>
+          <t>201012; 258552</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>192981; 250327</t>
+          <t>190360; 249008</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>165556; 212575</t>
+          <t>165556; 215675</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>206174; 256760</t>
+          <t>204215; 256830</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>193148; 247110</t>
+          <t>194689; 244015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>234501; 670320</t>
+          <t>236186; 665472</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>423515; 500432</t>
+          <t>429582; 502159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473557; 557781</t>
+          <t>470602; 551231</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>410893; 489099</t>
+          <t>412262; 485962</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>439904; 1034045</t>
+          <t>438997; 1078828</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54391; 86952</t>
+          <t>54430; 86739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97417; 137094</t>
+          <t>99443; 136985</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107575; 148954</t>
+          <t>109589; 150592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91369; 128925</t>
+          <t>89720; 126999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>146527; 188214</t>
+          <t>144237; 187806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>268625; 323101</t>
+          <t>272508; 326053</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>231766; 283962</t>
+          <t>232996; 285714</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>177947; 275442</t>
+          <t>187709; 281342</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208435; 261386</t>
+          <t>211933; 263456</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>382876; 452027</t>
+          <t>380883; 449327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>350571; 422249</t>
+          <t>350638; 420793</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>287922; 389709</t>
+          <t>285428; 386663</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25310; 48298</t>
+          <t>25768; 47399</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29957; 53059</t>
+          <t>30679; 54344</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22110; 42474</t>
+          <t>21915; 44095</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12879; 37325</t>
+          <t>14430; 40367</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>302251; 364748</t>
+          <t>301768; 365857</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>327835; 393789</t>
+          <t>331933; 393137</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>237880; 296813</t>
+          <t>234398; 294522</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>195687; 241393</t>
+          <t>193244; 241100</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>330510; 400918</t>
+          <t>332974; 400583</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367354; 437190</t>
+          <t>370110; 437777</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>263453; 327996</t>
+          <t>265051; 326763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>211913; 266187</t>
+          <t>213131; 267753</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>567263; 655230</t>
+          <t>563139; 651247</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>711116; 810739</t>
+          <t>712509; 812082</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>592936; 685461</t>
+          <t>594953; 689606</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>475002; 676807</t>
+          <t>478604; 679060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>844937; 945556</t>
+          <t>846188; 950323</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1105364; 1217453</t>
+          <t>1102762; 1219654</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>893170; 1002309</t>
+          <t>896221; 1002024</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>923410; 1625031</t>
+          <t>920647; 1651943</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1443364; 1570842</t>
+          <t>1440239; 1569765</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1841462; 2000922</t>
+          <t>1843794; 1997451</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1508770; 1653982</t>
+          <t>1518944; 1661624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1501321; 2350405</t>
+          <t>1492703; 2231858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 21,5</t>
+          <t>13,63; 21,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 20,33</t>
+          <t>13,24; 20,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,34</t>
+          <t>13,92; 21,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,62; 21,79</t>
+          <t>14,72; 21,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 27,39</t>
+          <t>17,72; 27,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 28,27</t>
+          <t>18,05; 28,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,41; 22,76</t>
+          <t>14,36; 22,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,28; 26,31</t>
+          <t>20,26; 26,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,4</t>
+          <t>16,44; 22,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 22,25</t>
+          <t>16,29; 22,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 20,68</t>
+          <t>15,19; 20,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,18; 23,14</t>
+          <t>18,33; 22,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 18,85</t>
+          <t>11,1; 18,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,13; 25,53</t>
+          <t>16,53; 25,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 20,99</t>
+          <t>13,04; 21,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 19,67</t>
+          <t>12,83; 19,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,68; 30,63</t>
+          <t>21,29; 30,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,18; 38,22</t>
+          <t>27,4; 38,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 28,91</t>
+          <t>20,01; 29,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,17; 28,61</t>
+          <t>21,45; 29,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 23,77</t>
+          <t>17,23; 23,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,66; 29,41</t>
+          <t>22,74; 29,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 23,61</t>
+          <t>17,55; 23,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 22,65</t>
+          <t>17,86; 23,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,74; 21,53</t>
+          <t>15,08; 21,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,35; 29,18</t>
+          <t>22,09; 29,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 25,36</t>
+          <t>18,31; 25,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 24,84</t>
+          <t>19,28; 27,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,28; 32,39</t>
+          <t>19,49; 32,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,77; 41,26</t>
+          <t>28,86; 41,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,53; 39,97</t>
+          <t>23,31; 38,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,07; 31,09</t>
+          <t>20,78; 30,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,88</t>
+          <t>16,66; 22,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,0; 31,46</t>
+          <t>25,16; 31,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,31</t>
+          <t>20,27; 27,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 25,18</t>
+          <t>20,85; 27,25</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 24,05</t>
+          <t>19,66; 24,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,97; 27,24</t>
+          <t>21,72; 27,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 22,49</t>
+          <t>17,82; 22,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,49; 24,18</t>
+          <t>18,41; 23,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 30,19</t>
+          <t>23,26; 30,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,64; 33,5</t>
+          <t>26,57; 33,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,57; 29,55</t>
+          <t>23,32; 29,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,2; 68,2</t>
+          <t>22,92; 28,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,0; 25,72</t>
+          <t>21,64; 25,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 28,63</t>
+          <t>24,5; 28,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 24,6</t>
+          <t>20,92; 24,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,89; 53,79</t>
+          <t>20,95; 24,53</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,53; 24,74</t>
+          <t>15,1; 24,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,48; 26,83</t>
+          <t>19,39; 26,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 24,26</t>
+          <t>17,6; 23,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 27,0</t>
+          <t>18,19; 25,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,36; 33,02</t>
+          <t>25,19; 33,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,78; 42,82</t>
+          <t>35,43; 42,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,56; 38,7</t>
+          <t>31,35; 38,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,44; 33,63</t>
+          <t>30,15; 35,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,05; 28,66</t>
+          <t>22,81; 28,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,94; 35,32</t>
+          <t>30,13; 35,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,8; 30,96</t>
+          <t>25,9; 30,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,84; 29,58</t>
+          <t>25,88; 30,36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 15,9</t>
+          <t>8,51; 16,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,5; 20,36</t>
+          <t>11,42; 20,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 15,36</t>
+          <t>7,71; 15,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,78</t>
+          <t>7,36; 19,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,17; 29,3</t>
+          <t>24,27; 29,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,92; 35,44</t>
+          <t>29,86; 35,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 27,22</t>
+          <t>21,69; 27,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,68; 32,03</t>
+          <t>25,49; 31,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,52; 25,89</t>
+          <t>21,63; 25,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,89; 31,81</t>
+          <t>26,79; 31,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,36; 23,87</t>
+          <t>19,39; 23,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,46; 26,96</t>
+          <t>22,25; 27,68</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,22; 19,91</t>
+          <t>17,38; 20,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,82; 23,73</t>
+          <t>20,87; 23,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,37</t>
+          <t>17,57; 20,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,21</t>
+          <t>18,1; 20,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,05; 28,13</t>
+          <t>25,05; 27,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,06; 34,36</t>
+          <t>31,16; 34,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,38; 28,37</t>
+          <t>25,22; 28,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 46,41</t>
+          <t>26,13; 28,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,66; 23,61</t>
+          <t>21,68; 23,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,45; 28,65</t>
+          <t>26,42; 28,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,96; 24,02</t>
+          <t>21,93; 24,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,57; 32,25</t>
+          <t>22,64; 24,58</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91982</t>
+          <t>97903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>102821</t>
+          <t>114446</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>194803</t>
+          <t>212349</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67341; 101865</t>
+          <t>64554; 101483</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57989; 88889</t>
+          <t>57901; 88712</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59438; 91561</t>
+          <t>59747; 92279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73541; 109618</t>
+          <t>80707; 118161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53914; 84008</t>
+          <t>54332; 83898</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56763; 88909</t>
+          <t>56764; 88602</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50022; 79003</t>
+          <t>49853; 78338</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86036; 117409</t>
+          <t>98634; 131079</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131493; 174785</t>
+          <t>128312; 172767</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>120640; 167248</t>
+          <t>122449; 169174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116062; 160469</t>
+          <t>117867; 159989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>172613; 219606</t>
+          <t>189682; 237848</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73026</t>
+          <t>77098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93718</t>
+          <t>106641</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>166744</t>
+          <t>183739</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41460; 69162</t>
+          <t>40729; 68097</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71759; 106936</t>
+          <t>69220; 105916</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48514; 79188</t>
+          <t>49179; 80124</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58497; 88785</t>
+          <t>61861; 94396</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80618; 113906</t>
+          <t>79156; 112433</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91855; 129198</t>
+          <t>92622; 130156</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74199; 107625</t>
+          <t>74488; 108858</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80877; 109292</t>
+          <t>90616; 124610</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131519; 175646</t>
+          <t>127276; 171741</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171501; 222581</t>
+          <t>172107; 223498</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131962; 176974</t>
+          <t>131541; 177300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>147465; 188797</t>
+          <t>161563; 209025</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98869</t>
+          <t>108997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42929</t>
+          <t>47787</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>141797</t>
+          <t>156784</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79965; 116762</t>
+          <t>81817; 117160</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140655; 183635</t>
+          <t>139025; 185193</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95414; 132382</t>
+          <t>95581; 132330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33728; 165268</t>
+          <t>90346; 126736</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32353; 54346</t>
+          <t>32705; 55066</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74846; 107342</t>
+          <t>75076; 107361</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40756; 66396</t>
+          <t>38720; 64194</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34966; 51584</t>
+          <t>38738; 57614</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119675; 162494</t>
+          <t>118341; 161433</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222373; 279827</t>
+          <t>223793; 280227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143126; 187920</t>
+          <t>139476; 186179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69359; 209286</t>
+          <t>136583; 178541</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217516</t>
+          <t>234636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>395903</t>
+          <t>218090</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>613419</t>
+          <t>452726</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>244263; 297787</t>
+          <t>243428; 300150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254655; 315669</t>
+          <t>251711; 315182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>201012; 258552</t>
+          <t>204889; 258544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190360; 249008</t>
+          <t>207378; 262628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>165556; 215675</t>
+          <t>166116; 217874</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>204215; 256830</t>
+          <t>203721; 255552</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>194689; 244015</t>
+          <t>192558; 243867</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>236186; 665472</t>
+          <t>196841; 242044</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>429582; 502159</t>
+          <t>422604; 498635</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>470602; 551231</t>
+          <t>471700; 555588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>412262; 485962</t>
+          <t>413321; 485275</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>438997; 1078828</t>
+          <t>415890; 486983</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107481</t>
+          <t>121892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>241294</t>
+          <t>268795</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>348775</t>
+          <t>390687</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54430; 86739</t>
+          <t>52943; 84991</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99443; 136985</t>
+          <t>98984; 137468</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109589; 150592</t>
+          <t>109228; 148491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89720; 126999</t>
+          <t>102420; 143132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>144237; 187806</t>
+          <t>143280; 189630</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>272508; 326053</t>
+          <t>269776; 325398</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>232996; 285714</t>
+          <t>231436; 285722</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>187709; 281342</t>
+          <t>248998; 291274</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>211933; 263456</t>
+          <t>209654; 263833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>380883; 449327</t>
+          <t>383313; 448539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>350638; 420793</t>
+          <t>352020; 418969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>285428; 386663</t>
+          <t>359511; 421733</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>217472</t>
+          <t>237279</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>240168</t>
+          <t>265804</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25768; 47399</t>
+          <t>25381; 48840</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30679; 54344</t>
+          <t>30474; 53444</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21915; 44095</t>
+          <t>22133; 43191</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14430; 40367</t>
+          <t>17454; 45244</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>301768; 365857</t>
+          <t>303109; 365661</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>331933; 393137</t>
+          <t>331296; 393142</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>234398; 294522</t>
+          <t>234696; 294370</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>193244; 241100</t>
+          <t>212866; 261654</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>332974; 400583</t>
+          <t>334658; 400103</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>370110; 437777</t>
+          <t>368712; 436308</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>265051; 326763</t>
+          <t>265538; 326179</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>213131; 267753</t>
+          <t>238660; 296878</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>611570</t>
+          <t>669051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1094137</t>
+          <t>993038</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1705706</t>
+          <t>1662089</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>563139; 651247</t>
+          <t>568462; 655600</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>712509; 812082</t>
+          <t>714067; 815889</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>594953; 689606</t>
+          <t>595022; 685424</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>478604; 679060</t>
+          <t>620103; 715374</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>846188; 950323</t>
+          <t>846340; 944990</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1102762; 1219654</t>
+          <t>1106139; 1217870</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>896221; 1002024</t>
+          <t>890786; 1002304</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>920647; 1651943</t>
+          <t>944726; 1040737</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1440239; 1569765</t>
+          <t>1441486; 1576101</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1843794; 1997451</t>
+          <t>1841853; 1998913</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1518944; 1661624</t>
+          <t>1516656; 1664060</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1492703; 2231858</t>
+          <t>1594154; 1730781</t>
         </is>
       </c>
     </row>
